--- a/velddata_mosselkartering_midden-nederland_2024.xlsx
+++ b/velddata_mosselkartering_midden-nederland_2024.xlsx
@@ -15178,14 +15178,8 @@
       <c r="B90" s="76" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="17" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D90" s="73" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
+      <c r="C90" s="17"/>
+      <c r="D90" s="73"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="77"/>
